--- a/artfynd/S 1474-2025 artfynd.xlsx
+++ b/artfynd/S 1474-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395923</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82396250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557816</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,6 +1515,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557415</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1599,6 +1639,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82396284</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1717,6 +1762,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82396276</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1835,6 +1885,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565915</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395794</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2067,6 +2127,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556728</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2181,6 +2246,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557493</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82564829</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565303</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2523,6 +2603,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568359</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2641,6 +2726,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556626</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2759,6 +2849,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557628</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2877,6 +2972,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82564977</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2988,6 +3088,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74210077</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3099,6 +3204,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75175023</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3217,6 +3327,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395660</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3335,6 +3450,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395667</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3453,6 +3573,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82395898</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3571,6 +3696,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82396559</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3689,6 +3819,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82399830</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3807,6 +3942,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82399832</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3925,6 +4065,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82399983</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4043,6 +4188,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556469</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4161,6 +4311,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556489</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4279,6 +4434,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556500</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4397,6 +4557,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556513</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4515,6 +4680,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556529</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4633,6 +4803,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556550</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4751,6 +4926,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556567</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4869,6 +5049,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556577</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4987,6 +5172,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556599</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5105,6 +5295,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556609</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5223,6 +5418,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556617</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5341,6 +5541,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556637</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5459,6 +5664,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556655</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5577,6 +5787,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82556677</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5695,6 +5910,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557055</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5813,6 +6033,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557073</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5931,6 +6156,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557099</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6049,6 +6279,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557118</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6167,6 +6402,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557135</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6285,6 +6525,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557153</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6403,6 +6648,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557171</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6521,6 +6771,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557207</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6639,6 +6894,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557231</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6757,6 +7017,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557252</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6875,6 +7140,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557271</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6993,6 +7263,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557301</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7111,6 +7386,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557317</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7229,6 +7509,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557340</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7347,6 +7632,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557360</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7465,6 +7755,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557377</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7583,6 +7878,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557407</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7701,6 +8001,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557602</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7819,6 +8124,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557611</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7937,6 +8247,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557622</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8055,6 +8370,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557646</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8173,6 +8493,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557871</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8291,6 +8616,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557879</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8409,6 +8739,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557882</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8527,6 +8862,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82557885</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8645,6 +8985,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565026</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8763,6 +9108,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565109</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8881,6 +9231,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565138</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8999,6 +9354,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565153</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9117,6 +9477,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565176</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9235,6 +9600,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565604</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9353,6 +9723,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565690</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9471,6 +9846,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565767</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9589,6 +9969,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565797</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9707,6 +10092,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565819</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9825,6 +10215,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565846</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9943,6 +10338,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565867</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10061,6 +10461,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565881</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10179,6 +10584,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565903</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10297,6 +10707,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82565962</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10415,6 +10830,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82566034</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10533,6 +10953,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82566118</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10651,6 +11076,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82566220</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10769,6 +11199,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82566286</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10887,6 +11322,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82566377</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11005,6 +11445,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568181</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11123,6 +11568,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568299</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11241,6 +11691,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568335</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11359,6 +11814,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568493</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11477,6 +11937,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568501</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11595,8 +12060,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82568508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>